--- a/data/trans_orig/IP31KM13_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM13_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>50258</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>46054</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>52657</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>93,56%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>85,74%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>98,03%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>46475</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>35328</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>51000</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>86,55%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>65,79%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>94,97%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>54112</t>
+          <t>41264</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48651</t>
+          <t>37024</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56794</t>
+          <t>43739</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>100587</t>
+          <t>91522</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>89615</t>
+          <t>86000</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106376</t>
+          <t>95132</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3457</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7661</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>14,26%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7224</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2699</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18371</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>13,45%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>34,21%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9694</t>
+          <t>8881</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>11456</t>
+          <t>8098</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5667</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22428</t>
+          <t>13620</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>577</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>418989</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>388124</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>432576</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>89,83%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>83,21%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>92,74%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>583</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>422313</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>410477</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>430686</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>93,47%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>90,85%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>95,32%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>577</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>454505</t>
+          <t>394322</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>422492</t>
+          <t>384389</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>469526</t>
+          <t>402889</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>876818</t>
+          <t>813312</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>836402</t>
+          <t>777177</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>893093</t>
+          <t>828494</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>92,98%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>47434</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>33847</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>78299</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>10,17%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>16,79%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>29519</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>21146</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>41355</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,53%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,15%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>50745</t>
+          <t>30344</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35724</t>
+          <t>21777</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82758</t>
+          <t>40277</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>80264</t>
+          <t>77778</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>63989</t>
+          <t>62596</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>120680</t>
+          <t>113913</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>625</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>156764</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>149589</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>161346</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>94,05%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>89,74%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>96,8%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>132948</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>125743</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>137678</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>90,94%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>86,02%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>94,18%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>170577</t>
+          <t>133721</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>163454</t>
+          <t>126360</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>175539</t>
+          <t>139049</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>303524</t>
+          <t>290484</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>295099</t>
+          <t>281946</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>311152</t>
+          <t>297630</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,84%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9922</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5340</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>17097</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5,95%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>10,26%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>13238</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8508</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>20443</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>9,06%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>13,98%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10562</t>
+          <t>13419</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17685</t>
+          <t>20780</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>23800</t>
+          <t>23341</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16172</t>
+          <t>16195</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32225</t>
+          <t>31879</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>626011</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>595829</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>640733</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>91,15%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>86,75%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>93,29%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>845</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>601736</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>586009</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>613006</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>92,33%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>89,92%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>94,06%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>869</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>679193</t>
+          <t>569306</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>638897</t>
+          <t>556389</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>695737</t>
+          <t>579904</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1280929</t>
+          <t>1195318</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1241390</t>
+          <t>1166263</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1300440</t>
+          <t>1214404</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>60813</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>46091</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>90995</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>8,85%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6,71%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>13,25%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>49981</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>38711</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>65708</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5,94%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>10,08%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>65540</t>
+          <t>48405</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48996</t>
+          <t>37807</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>105836</t>
+          <t>61322</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>115521</t>
+          <t>109217</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>96010</t>
+          <t>90131</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>155060</t>
+          <t>138272</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
